--- a/Extracted_data_analysis/tropical/Output-Transformed_data/sampling_unit_tot.xlsx
+++ b/Extracted_data_analysis/tropical/Output-Transformed_data/sampling_unit_tot.xlsx
@@ -437,7 +437,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4">
@@ -492,7 +492,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -503,7 +503,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
